--- a/erp-server/erp-server-file/src/main/resources/excel/oms/SoReceipt.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/SoReceipt.xlsx
@@ -119,7 +119,7 @@
     <t>{.receiptAmount}</t>
   </si>
   <si>
-    <t>{.receiptAccount}</t>
+    <t>{.receiptAccountName}</t>
   </si>
   <si>
     <t>{.receiptDate}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/SoReceipt.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/SoReceipt.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>收款编号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>客户</t>
   </si>
   <si>
+    <t>销售组织</t>
+  </si>
+  <si>
     <t>单据状态</t>
   </si>
   <si>
@@ -99,6 +102,9 @@
   </si>
   <si>
     <t>{.customerName}</t>
+  </si>
+  <si>
+    <t>{.salesOrgName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -1123,25 +1129,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="7" width="20.125" customWidth="1"/>
-    <col min="8" max="10" width="20.625" customWidth="1"/>
-    <col min="11" max="11" width="20.875" customWidth="1"/>
-    <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="13.125" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="22.925" customWidth="1"/>
-    <col min="16" max="16" width="15.2083333333333" customWidth="1"/>
-    <col min="17" max="17" width="11.1916666666667" customWidth="1"/>
-    <col min="18" max="18" width="13.2583333333333" customWidth="1"/>
-    <col min="19" max="19" width="12.925" customWidth="1"/>
-    <col min="20" max="20" width="11.625" customWidth="1"/>
-    <col min="21" max="21" width="15.9666666666667" customWidth="1"/>
+    <col min="1" max="8" width="20.125" customWidth="1"/>
+    <col min="9" max="11" width="20.625" customWidth="1"/>
+    <col min="12" max="12" width="20.875" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="13.125" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
+    <col min="16" max="16" width="22.925" customWidth="1"/>
+    <col min="17" max="17" width="15.2083333333333" customWidth="1"/>
+    <col min="18" max="18" width="11.1916666666667" customWidth="1"/>
+    <col min="19" max="19" width="13.2583333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.925" customWidth="1"/>
+    <col min="21" max="21" width="11.625" customWidth="1"/>
+    <col min="22" max="22" width="15.9666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1205,70 +1211,76 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/oms/SoReceipt.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/oms/SoReceipt.xlsx
@@ -46,7 +46,7 @@
     <t>收款金额</t>
   </si>
   <si>
-    <t>手续费</t>
+    <t>银行手续费</t>
   </si>
   <si>
     <t>收款账号</t>
@@ -115,7 +115,7 @@
     <t>{.receiptAmount}</t>
   </si>
   <si>
-    <t>{.serviceFee}</t>
+    <t>{.bankServiceFee}</t>
   </si>
   <si>
     <t>{.receiptAccountName}</t>
